--- a/output/20261002_MK_2026_DACH_Clipping_Report___Analysis.xlsx
+++ b/output/20261002_MK_2026_DACH_Clipping_Report___Analysis.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46297.48504167596</v>
+        <v>46297.73901472352</v>
       </c>
     </row>
     <row r="8">

--- a/output/20261002_MK_2026_DACH_Clipping_Report___Analysis.xlsx
+++ b/output/20261002_MK_2026_DACH_Clipping_Report___Analysis.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46297.73901472352</v>
+        <v>46297.9181869597</v>
       </c>
     </row>
     <row r="8">
